--- a/data/raw/input_default_values_sources.xlsx
+++ b/data/raw/input_default_values_sources.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rotenle/Documents/MetC_Locals/MTS/climate-multimodal-measures/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E1F41C-042C-B24F-A8C2-B69C8C6C68F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA389E9-EF2D-004A-844B-D1F6E94FB90C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="500" windowWidth="24400" windowHeight="15580" xr2:uid="{9F3C916E-6CEA-B948-AC4B-7F24B434A037}"/>
+    <workbookView xWindow="1660" yWindow="1240" windowWidth="33980" windowHeight="15580" xr2:uid="{9F3C916E-6CEA-B948-AC4B-7F24B434A037}"/>
   </bookViews>
   <sheets>
     <sheet name="input_default_values" sheetId="1" r:id="rId1"/>
